--- a/tests/perf_v2/perf_history/v2.5/detection/DETECTION-raw-Vitens-Aeromonas.xlsx
+++ b/tests/perf_v2/perf_history/v2.5/detection/DETECTION-raw-Vitens-Aeromonas.xlsx
@@ -7,15 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="atss_mobilenetv2" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="atss_resnext101" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dfine_x" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_101" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_18" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_50" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtmdet_tiny" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ssd_mobilenetv2" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_l" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="atss_resnext101" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dfine_x" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_101" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_18" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_50" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ssd_mobilenetv2" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_l" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="atss_mobilenetv2" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtmdet_tiny" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_s" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_tiny" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_x" sheetId="12" state="visible" r:id="rId12"/>
@@ -596,56 +596,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C2" t="n">
-        <v>492.7823739051819</v>
+        <v>938.6961586475372</v>
       </c>
       <c r="D2" t="n">
-        <v>6.849999904632568</v>
+        <v>15.39999961853027</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4864118710944527</v>
+        <v>0.5080897067044232</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8366873264312744</v>
+        <v>0.8632606863975525</v>
       </c>
       <c r="G2" t="n">
-        <v>0.905825674533844</v>
+        <v>0.9182335138320924</v>
       </c>
       <c r="H2" t="n">
-        <v>0.905825674533844</v>
+        <v>0.919107973575592</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9070568084716796</v>
+        <v>0.9192982316017152</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3278024196624756</v>
+        <v>0.1877455115318298</v>
       </c>
       <c r="K2" t="n">
-        <v>73.01832604408264</v>
+        <v>391.4669995307922</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1133985159532079</v>
+        <v>0.1178738711015233</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3368128920501133</v>
+        <v>0.640735923119311</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3145395674795475</v>
+        <v>0.3477375192462273</v>
       </c>
       <c r="O2" t="n">
-        <v>6.01012134552002</v>
+        <v>6.247315168380737</v>
       </c>
       <c r="P2" t="n">
-        <v>17.85108327865601</v>
+        <v>33.95900392532349</v>
       </c>
       <c r="Q2" t="n">
-        <v>16.67059707641602</v>
+        <v>18.43008852005005</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250627-180617</t>
+          <t>20250726-053502</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -670,22 +670,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -717,56 +717,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C3" t="n">
-        <v>365.562046289444</v>
+        <v>938.4433901309968</v>
       </c>
       <c r="D3" t="n">
-        <v>6.690000057220459</v>
+        <v>15.39999961853027</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4638315480330894</v>
+        <v>0.5077033912813341</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8332052230834961</v>
+        <v>0.869016706943512</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9031111001968384</v>
+        <v>0.9224062561988832</v>
       </c>
       <c r="H3" t="n">
-        <v>0.903598427772522</v>
+        <v>0.9215344190597534</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9037693738937378</v>
+        <v>0.9208570122718812</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2948665022850036</v>
+        <v>0.1839452981948852</v>
       </c>
       <c r="K3" t="n">
-        <v>72.97705483436584</v>
+        <v>433.614351272583</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1094226342327189</v>
+        <v>0.1169138224619739</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3289148987464185</v>
+        <v>0.6554756479443244</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3193834187849512</v>
+        <v>0.3754017263088586</v>
       </c>
       <c r="O3" t="n">
-        <v>5.799399614334106</v>
+        <v>6.196432590484619</v>
       </c>
       <c r="P3" t="n">
-        <v>17.43248963356018</v>
+        <v>34.74020934104919</v>
       </c>
       <c r="Q3" t="n">
-        <v>16.92732119560242</v>
+        <v>19.89629149436951</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250627-181706</t>
+          <t>20250726-055910</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -791,22 +791,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -838,56 +838,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="C4" t="n">
-        <v>418.8017570972443</v>
+        <v>1232.075493574142</v>
       </c>
       <c r="D4" t="n">
-        <v>7.210000038146973</v>
+        <v>15.39000034332275</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4873544313013553</v>
+        <v>0.5088854334792312</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8269375562667847</v>
+        <v>0.8714338541030884</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8818897604942322</v>
+        <v>0.9173589944839478</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8824814558029175</v>
+        <v>0.9164844751358032</v>
       </c>
       <c r="I4" t="n">
-        <v>0.882867157459259</v>
+        <v>0.9187027812004088</v>
       </c>
       <c r="J4" t="n">
-        <v>0.326488196849823</v>
+        <v>0.1813338696956634</v>
       </c>
       <c r="K4" t="n">
-        <v>71.84800410270691</v>
+        <v>373.9492545127869</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1128520605699071</v>
+        <v>0.1172663220819437</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3298849789601452</v>
+        <v>0.6726168551534977</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3210471126268495</v>
+        <v>0.3676271438598633</v>
       </c>
       <c r="O4" t="n">
-        <v>5.981159210205078</v>
+        <v>6.215115070343018</v>
       </c>
       <c r="P4" t="n">
-        <v>17.4839038848877</v>
+        <v>35.64869332313538</v>
       </c>
       <c r="Q4" t="n">
-        <v>17.01549696922302</v>
+        <v>19.48423862457276</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250627-182547</t>
+          <t>20250726-062350</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -912,22 +912,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -959,56 +959,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="C5" t="n">
-        <v>570.5052013397217</v>
+        <v>889.7630529403687</v>
       </c>
       <c r="D5" t="n">
-        <v>6.860000133514404</v>
+        <v>15.52000045776367</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4828944477167996</v>
+        <v>0.5082413724490574</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8375339508056641</v>
+        <v>0.8681937456130981</v>
       </c>
       <c r="G5" t="n">
-        <v>0.908450722694397</v>
+        <v>0.9207183718681335</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9066901206970216</v>
+        <v>0.9215256571769714</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9050132036209106</v>
+        <v>0.9227392673492432</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3125357627868652</v>
+        <v>0.1828660368919372</v>
       </c>
       <c r="K5" t="n">
-        <v>77.45805501937866</v>
+        <v>445.4474587440491</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1095531976447915</v>
+        <v>0.1168164757062804</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3311687145593031</v>
+        <v>0.6508985420442978</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3275613829774677</v>
+        <v>0.3648492075362295</v>
       </c>
       <c r="O5" t="n">
-        <v>5.80631947517395</v>
+        <v>6.191273212432861</v>
       </c>
       <c r="P5" t="n">
-        <v>17.55194187164307</v>
+        <v>34.49762272834778</v>
       </c>
       <c r="Q5" t="n">
-        <v>17.36075329780579</v>
+        <v>19.33700799942017</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250627-183521</t>
+          <t>20250726-065220</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1033,22 +1033,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1080,56 +1080,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="C6" t="n">
-        <v>391.9583246707916</v>
+        <v>1399.024042129517</v>
       </c>
       <c r="D6" t="n">
-        <v>6.860000133514404</v>
+        <v>15.52999973297119</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5020293891429901</v>
+        <v>0.5141474897211248</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8460966348648071</v>
+        <v>0.8750918507575989</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9007833003997804</v>
+        <v>0.9230769276618958</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9003914594650269</v>
+        <v>0.9235528111457824</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8975609540939331</v>
+        <v>0.923212707042694</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2807487845420837</v>
+        <v>0.1829225420951843</v>
       </c>
       <c r="K6" t="n">
-        <v>73.52596306800842</v>
+        <v>420.1706054210663</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1119329614459343</v>
+        <v>0.1213540401098863</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3340092020214729</v>
+        <v>0.69228621248929</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3209806658187003</v>
+        <v>0.3687567440968639</v>
       </c>
       <c r="O6" t="n">
-        <v>5.932446956634521</v>
+        <v>6.431764125823975</v>
       </c>
       <c r="P6" t="n">
-        <v>17.70248770713806</v>
+        <v>36.69116926193237</v>
       </c>
       <c r="Q6" t="n">
-        <v>17.01197528839111</v>
+        <v>19.54410743713379</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250627-184722</t>
+          <t>20250726-071628</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1154,22 +1154,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -3680,56 +3680,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="C2" t="n">
-        <v>631.1343314647675</v>
+        <v>4369.929616928101</v>
       </c>
       <c r="D2" t="n">
-        <v>9.729999542236328</v>
+        <v>21.13999938964844</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3093658492371842</v>
+        <v>3.113733564104353</v>
       </c>
       <c r="F2" t="n">
-        <v>0.864745020866394</v>
+        <v>0.9283625483512878</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9221978187561036</v>
+        <v>0.951843798160553</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9205094575881958</v>
+        <v>0.9509761333465576</v>
       </c>
       <c r="I2" t="n">
-        <v>0.918018400669098</v>
+        <v>0.9475963711738586</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1259105205535888</v>
+        <v>0.5075083374977112</v>
       </c>
       <c r="K2" t="n">
-        <v>565.7306334972382</v>
+        <v>677.7210118770599</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1158319509254311</v>
+        <v>0.1973746047829682</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6609726986795101</v>
+        <v>0.4321634364577959</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3652406008738392</v>
+        <v>0.4254335817301048</v>
       </c>
       <c r="O2" t="n">
-        <v>6.139093399047852</v>
+        <v>10.46085405349731</v>
       </c>
       <c r="P2" t="n">
-        <v>35.03155303001404</v>
+        <v>22.90466213226318</v>
       </c>
       <c r="Q2" t="n">
-        <v>19.35775184631348</v>
+        <v>22.54797983169556</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250629-114131</t>
+          <t>20250725-015512</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -3754,22 +3754,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -3801,56 +3801,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C3" t="n">
-        <v>811.9008765220642</v>
+        <v>4901.940502882004</v>
       </c>
       <c r="D3" t="n">
-        <v>9.75</v>
+        <v>20.54000091552734</v>
       </c>
       <c r="E3" t="n">
-        <v>0.309525265338573</v>
+        <v>3.135114366357977</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8668171763420105</v>
+        <v>0.9310725927352904</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9172866344451904</v>
+        <v>0.9470056295394896</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9167397022247314</v>
+        <v>0.945945918560028</v>
       </c>
       <c r="I3" t="n">
-        <v>0.916191339492798</v>
+        <v>0.9485614895820618</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1285234987735748</v>
+        <v>0.4913135170936584</v>
       </c>
       <c r="K3" t="n">
-        <v>411.3317489624024</v>
+        <v>617.7132868766785</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1236839294433593</v>
+        <v>0.1845800876617431</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6726023026232449</v>
+        <v>0.4432038091263681</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3737231290565346</v>
+        <v>0.4222645309736144</v>
       </c>
       <c r="O3" t="n">
-        <v>6.555248260498047</v>
+        <v>9.782744646072388</v>
       </c>
       <c r="P3" t="n">
-        <v>35.64792203903198</v>
+        <v>23.48980188369751</v>
       </c>
       <c r="Q3" t="n">
-        <v>19.80732583999633</v>
+        <v>22.38002014160156</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250629-120328</t>
+          <t>20250725-032121</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -3875,22 +3875,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -3922,56 +3922,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="C4" t="n">
-        <v>759.7946910858154</v>
+        <v>5272.360812187195</v>
       </c>
       <c r="D4" t="n">
-        <v>9.779999732971191</v>
+        <v>21.47999954223633</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3088851756519741</v>
+        <v>3.127370765653707</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8632128238677979</v>
+        <v>0.9320247173309326</v>
       </c>
       <c r="G4" t="n">
-        <v>0.921936333179474</v>
+        <v>0.951676070690155</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9215344190597534</v>
+        <v>0.9512619376182556</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9210640788078308</v>
+        <v>0.9477806687355042</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1577886790037155</v>
+        <v>0.5090490579605103</v>
       </c>
       <c r="K4" t="n">
-        <v>423.1792304515839</v>
+        <v>624.7588992118835</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1298046831814747</v>
+        <v>0.1926761438261788</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6571314559792573</v>
+        <v>0.4248692674456902</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3815784499330341</v>
+        <v>0.4175559079871987</v>
       </c>
       <c r="O4" t="n">
-        <v>6.879648208618164</v>
+        <v>10.21183562278748</v>
       </c>
       <c r="P4" t="n">
-        <v>34.82796716690063</v>
+        <v>22.51807117462159</v>
       </c>
       <c r="Q4" t="n">
-        <v>20.22365784645081</v>
+        <v>22.13046312332153</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250629-122538</t>
+          <t>20250725-045527</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -3996,22 +3996,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -4043,56 +4043,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C5" t="n">
-        <v>973.1579999923706</v>
+        <v>4719.270351171494</v>
       </c>
       <c r="D5" t="n">
-        <v>9.779999732971191</v>
+        <v>20.93000030517578</v>
       </c>
       <c r="E5" t="n">
-        <v>0.310026642000466</v>
+        <v>3.089453772262291</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8631421327590942</v>
+        <v>0.9206695556640624</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9171366691589355</v>
+        <v>0.9438886642456056</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9205384254455566</v>
+        <v>0.943018674850464</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9156938791275024</v>
+        <v>0.94030499458313</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1386824697256088</v>
+        <v>0.4753372371196747</v>
       </c>
       <c r="K5" t="n">
-        <v>444.7392163276672</v>
+        <v>618.4258389472961</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1255945124716129</v>
+        <v>0.1846178027818787</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6732781158303315</v>
+        <v>0.4415310778707828</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3568492160653168</v>
+        <v>0.4233666051108882</v>
       </c>
       <c r="O5" t="n">
-        <v>6.656509160995483</v>
+        <v>9.784743547439575</v>
       </c>
       <c r="P5" t="n">
-        <v>35.68374013900757</v>
+        <v>23.40114712715149</v>
       </c>
       <c r="Q5" t="n">
-        <v>18.91300845146179</v>
+        <v>22.43843007087708</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250629-124707</t>
+          <t>20250725-063556</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -4117,22 +4117,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -4164,56 +4164,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C6" t="n">
-        <v>630.547828912735</v>
+        <v>3830.764610290527</v>
       </c>
       <c r="D6" t="n">
-        <v>9.869999885559082</v>
+        <v>22.29999923706055</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3104028887039906</v>
+        <v>3.098723162052244</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8679806590080261</v>
+        <v>0.926061511039734</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9141104221343994</v>
+        <v>0.946678340435028</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9149868488311768</v>
+        <v>0.9474141597747804</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9162647724151612</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1338410824537277</v>
+        <v>0.470289409160614</v>
       </c>
       <c r="K6" t="n">
-        <v>404.8866517543793</v>
+        <v>613.3690655231476</v>
       </c>
       <c r="L6" t="n">
-        <v>0.123931605860872</v>
+        <v>0.183973694747349</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6507422069333634</v>
+        <v>0.4409571953539578</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3565284441102226</v>
+        <v>0.3910801320705773</v>
       </c>
       <c r="O6" t="n">
-        <v>6.568375110626221</v>
+        <v>9.750605821609495</v>
       </c>
       <c r="P6" t="n">
-        <v>34.48933696746826</v>
+        <v>23.37073135375977</v>
       </c>
       <c r="Q6" t="n">
-        <v>18.8960075378418</v>
+        <v>20.7272469997406</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250629-131246</t>
+          <t>20250725-080705</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -4238,22 +4238,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -4451,56 +4451,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="C2" t="n">
-        <v>1492.179150104523</v>
+        <v>4953.195133447647</v>
       </c>
       <c r="D2" t="n">
-        <v>15.3100004196167</v>
+        <v>11.57999992370606</v>
       </c>
       <c r="E2" t="n">
-        <v>3.064113199710846</v>
+        <v>2.666756403751863</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9019033908843994</v>
+        <v>0.9369963407516479</v>
       </c>
       <c r="G2" t="n">
-        <v>0.928196132183075</v>
+        <v>0.952546775341034</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9295404553413392</v>
+        <v>0.953386127948761</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9229398369789124</v>
+        <v>0.946859896183014</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5259860157966614</v>
+        <v>0.5006208419799805</v>
       </c>
       <c r="K2" t="n">
-        <v>629.03182721138</v>
+        <v>203.4782776832581</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2106869355687555</v>
+        <v>0.189661682776685</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4475196127621633</v>
+        <v>0.4210471477148668</v>
       </c>
       <c r="N2" t="n">
-        <v>0.440503291363986</v>
+        <v>0.3908129278218971</v>
       </c>
       <c r="O2" t="n">
-        <v>11.16640758514404</v>
+        <v>10.05206918716431</v>
       </c>
       <c r="P2" t="n">
-        <v>23.71853947639465</v>
+        <v>22.31549882888794</v>
       </c>
       <c r="Q2" t="n">
-        <v>23.34667444229126</v>
+        <v>20.71308517456055</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250628-203700</t>
+          <t>20250727-110046</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -4525,22 +4525,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -4572,56 +4572,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="C3" t="n">
-        <v>1795.046883583069</v>
+        <v>5300.814284086227</v>
       </c>
       <c r="D3" t="n">
-        <v>15.39000034332275</v>
+        <v>11.22000026702881</v>
       </c>
       <c r="E3" t="n">
-        <v>3.178466370231227</v>
+        <v>2.658775295530047</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9064327478408812</v>
+        <v>0.9267585277557372</v>
       </c>
       <c r="G3" t="n">
-        <v>0.931506872177124</v>
+        <v>0.9536423683166504</v>
       </c>
       <c r="H3" t="n">
-        <v>0.929801344871521</v>
+        <v>0.9519188404083252</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9311562180519104</v>
+        <v>0.9483362436294556</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4684478342533111</v>
+        <v>0.4759760499000549</v>
       </c>
       <c r="K3" t="n">
-        <v>622.8581709861755</v>
+        <v>204.8908159732818</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1956752426219436</v>
+        <v>0.1880283445682165</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4403033751361775</v>
+        <v>0.4301089520724314</v>
       </c>
       <c r="N3" t="n">
-        <v>0.447214108593059</v>
+        <v>0.4070615948371167</v>
       </c>
       <c r="O3" t="n">
-        <v>10.37078785896301</v>
+        <v>9.96550226211548</v>
       </c>
       <c r="P3" t="n">
-        <v>23.33607888221741</v>
+        <v>22.79577445983887</v>
       </c>
       <c r="Q3" t="n">
-        <v>23.70234775543213</v>
+        <v>21.57426452636719</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250628-211418</t>
+          <t>20250727-122836</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -4646,22 +4646,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -4693,56 +4693,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C4" t="n">
-        <v>1510.517390489578</v>
+        <v>3328.843411684036</v>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>11.26000022888184</v>
       </c>
       <c r="E4" t="n">
-        <v>3.049316540360451</v>
+        <v>2.665696630111108</v>
       </c>
       <c r="F4" t="n">
-        <v>0.901147723197937</v>
+        <v>0.7342574000358582</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9251641035079956</v>
+        <v>0.7881278395652771</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9247593879699708</v>
+        <v>0.7853309512138367</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6545792818069458</v>
+        <v>0.5610598921775818</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5484442710876465</v>
+        <v>0.4803731441497803</v>
       </c>
       <c r="K4" t="n">
-        <v>625.9627327919006</v>
+        <v>203.4446172714233</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2183736990082938</v>
+        <v>0.2065457532990653</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4349678417421737</v>
+        <v>0.4511709393195386</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4302751928005578</v>
+        <v>0.3711856671099393</v>
       </c>
       <c r="O4" t="n">
-        <v>11.57380604743958</v>
+        <v>10.94692492485046</v>
       </c>
       <c r="P4" t="n">
-        <v>23.05329561233521</v>
+        <v>23.91205978393555</v>
       </c>
       <c r="Q4" t="n">
-        <v>22.80458521842957</v>
+        <v>19.67284035682678</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250628-215634</t>
+          <t>20250727-140216</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -4767,22 +4767,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -4814,56 +4814,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C5" t="n">
-        <v>1490.473859071732</v>
+        <v>4088.391978740692</v>
       </c>
       <c r="D5" t="n">
-        <v>15.14000034332275</v>
+        <v>10.67000007629394</v>
       </c>
       <c r="E5" t="n">
-        <v>3.100351542234421</v>
+        <v>2.666176542639732</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8928965926170349</v>
+        <v>0.930095672607422</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9270650148391724</v>
+        <v>0.9493007063865662</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9266578555107116</v>
+        <v>0.9489306211471558</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.946678340435028</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5353342890739441</v>
+        <v>0.4729072153568268</v>
       </c>
       <c r="K5" t="n">
-        <v>627.6631722450256</v>
+        <v>201.7307350635529</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2086167785356629</v>
+        <v>0.187827411687599</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4395134583959039</v>
+        <v>0.4411453795882891</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3867646343303176</v>
+        <v>0.3894720752284212</v>
       </c>
       <c r="O5" t="n">
-        <v>11.05668926239014</v>
+        <v>9.954852819442747</v>
       </c>
       <c r="P5" t="n">
-        <v>23.29421329498291</v>
+        <v>23.38070511817932</v>
       </c>
       <c r="Q5" t="n">
-        <v>20.49852561950684</v>
+        <v>20.64201998710632</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250628-223413</t>
+          <t>20250727-150258</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -4888,22 +4888,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -4935,56 +4935,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="C6" t="n">
-        <v>1793.71623635292</v>
+        <v>7060.240835428238</v>
       </c>
       <c r="D6" t="n">
-        <v>15.21000003814697</v>
+        <v>10.63000011444092</v>
       </c>
       <c r="E6" t="n">
-        <v>3.03611456155777</v>
+        <v>2.672471169914518</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7464228868484497</v>
+        <v>0.943853199481964</v>
       </c>
       <c r="G6" t="n">
-        <v>0.771946132183075</v>
+        <v>0.9576234221458436</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7704315781593323</v>
+        <v>0.9563318490982056</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7730004787445068</v>
+        <v>0.952673077583313</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5381741523742676</v>
+        <v>0.4864077270030975</v>
       </c>
       <c r="K6" t="n">
-        <v>621.2862966060638</v>
+        <v>208.1655929088593</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2081657625594229</v>
+        <v>0.1907788267675435</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4308123003761723</v>
+        <v>0.4320587437107878</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4328003154610688</v>
+        <v>0.3974017017292526</v>
       </c>
       <c r="O6" t="n">
-        <v>11.03278541564941</v>
+        <v>10.11127781867981</v>
       </c>
       <c r="P6" t="n">
-        <v>22.83305191993713</v>
+        <v>22.89911341667176</v>
       </c>
       <c r="Q6" t="n">
-        <v>22.93841671943665</v>
+        <v>21.06229019165039</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250628-231126</t>
+          <t>20250727-161623</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -5009,22 +5009,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -5222,56 +5222,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="C2" t="n">
-        <v>2407.388387203217</v>
+        <v>5264.385550022125</v>
       </c>
       <c r="D2" t="n">
-        <v>10.31999969482422</v>
+        <v>5.760000228881836</v>
       </c>
       <c r="E2" t="n">
-        <v>2.716715375582377</v>
+        <v>2.757268684666331</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9197781682014464</v>
+        <v>0.9133333563804626</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9470025897026062</v>
+        <v>0.9328590631484984</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9453909993171692</v>
+        <v>0.9338071942329408</v>
       </c>
       <c r="I2" t="n">
-        <v>0.939008355140686</v>
+        <v>0.9245785474777222</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4941352307796478</v>
+        <v>0.5890299081802368</v>
       </c>
       <c r="K2" t="n">
-        <v>249.7288217544556</v>
+        <v>92.81197810173036</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2059608495460366</v>
+        <v>0.2007538912431249</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4468964540733481</v>
+        <v>0.3485846924331953</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3936055066450586</v>
+        <v>0.3464235989552623</v>
       </c>
       <c r="O2" t="n">
-        <v>10.91592502593994</v>
+        <v>10.63995623588562</v>
       </c>
       <c r="P2" t="n">
-        <v>23.68551206588745</v>
+        <v>18.47498869895935</v>
       </c>
       <c r="Q2" t="n">
-        <v>20.86109185218811</v>
+        <v>18.3604507446289</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250630-082002</t>
+          <t>20250728-120814</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -5296,22 +5296,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -5343,56 +5343,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C3" t="n">
-        <v>2322.005934000016</v>
+        <v>3255.98717546463</v>
       </c>
       <c r="D3" t="n">
-        <v>9.930000305175779</v>
+        <v>5.590000152587891</v>
       </c>
       <c r="E3" t="n">
-        <v>2.764951383366304</v>
+        <v>2.745825595855713</v>
       </c>
       <c r="F3" t="n">
-        <v>0.903034806251526</v>
+        <v>0.8974739909172058</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9390997290611268</v>
+        <v>0.9220489859580994</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9395676851272584</v>
+        <v>0.9203935861587524</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9427312612533568</v>
+        <v>0.921716034412384</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5231568217277527</v>
+        <v>0.5508021116256714</v>
       </c>
       <c r="K3" t="n">
-        <v>258.0816919803619</v>
+        <v>92.38325572013856</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2042464535191374</v>
+        <v>0.1947533229611954</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4525155616256426</v>
+        <v>0.3531519556945225</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3908068324035069</v>
+        <v>0.3318732054728382</v>
       </c>
       <c r="O3" t="n">
-        <v>10.82506203651428</v>
+        <v>10.32192611694336</v>
       </c>
       <c r="P3" t="n">
-        <v>23.98332476615906</v>
+        <v>18.71705365180969</v>
       </c>
       <c r="Q3" t="n">
-        <v>20.71276211738586</v>
+        <v>17.58927989006042</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250630-090620</t>
+          <t>20250728-133900</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -5417,22 +5417,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -5464,56 +5464,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="C4" t="n">
-        <v>2712.024720191956</v>
+        <v>5957.88467669487</v>
       </c>
       <c r="D4" t="n">
-        <v>10.47000026702881</v>
+        <v>5.619999885559082</v>
       </c>
       <c r="E4" t="n">
-        <v>2.781758511066437</v>
+        <v>2.72700208805977</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9215469360351562</v>
+        <v>0.9150037169456482</v>
       </c>
       <c r="G4" t="n">
-        <v>0.940559446811676</v>
+        <v>0.9380453824996948</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9402008056640624</v>
+        <v>0.9370875358581544</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9348591566085817</v>
+        <v>0.9258605241775512</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4706272184848785</v>
+        <v>0.4421027600765228</v>
       </c>
       <c r="K4" t="n">
-        <v>235.0902655124664</v>
+        <v>92.32524681091309</v>
       </c>
       <c r="L4" t="n">
-        <v>0.199072963786575</v>
+        <v>0.1666390311043217</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4583639108909751</v>
+        <v>0.3587737083435058</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3963296638344818</v>
+        <v>0.3357375927691189</v>
       </c>
       <c r="O4" t="n">
-        <v>10.55086708068848</v>
+        <v>8.831868648529053</v>
       </c>
       <c r="P4" t="n">
-        <v>24.29328727722168</v>
+        <v>19.01500654220581</v>
       </c>
       <c r="Q4" t="n">
-        <v>21.00547218322754</v>
+        <v>17.79409241676331</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250630-095122</t>
+          <t>20250728-143628</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -5538,22 +5538,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -5585,56 +5585,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="C5" t="n">
-        <v>2213.633789777756</v>
+        <v>6231.942988634109</v>
       </c>
       <c r="D5" t="n">
-        <v>9.770000457763672</v>
+        <v>5.670000076293945</v>
       </c>
       <c r="E5" t="n">
-        <v>2.785187497735023</v>
+        <v>2.734884991937754</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6423670649528503</v>
+        <v>0.9107875823974608</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6753246784210205</v>
+        <v>0.9346866607666016</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6744897961616516</v>
+        <v>0.934628963470459</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6745955944061279</v>
+        <v>0.9272165894508362</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4659138917922973</v>
+        <v>0.6491677761077881</v>
       </c>
       <c r="K5" t="n">
-        <v>239.4001133441925</v>
+        <v>91.66545867919922</v>
       </c>
       <c r="L5" t="n">
-        <v>0.215222345208222</v>
+        <v>0.2028891680375585</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4562618012698191</v>
+        <v>0.34004212325474</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3881248168225558</v>
+        <v>0.3248665107871001</v>
       </c>
       <c r="O5" t="n">
-        <v>11.40678429603577</v>
+        <v>10.7531259059906</v>
       </c>
       <c r="P5" t="n">
-        <v>24.18187546730041</v>
+        <v>18.02223253250122</v>
       </c>
       <c r="Q5" t="n">
-        <v>20.57061529159546</v>
+        <v>17.21792507171631</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250630-104232</t>
+          <t>20250728-161840</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -5644,7 +5644,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -5659,22 +5659,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -5706,56 +5706,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="C6" t="n">
-        <v>2207.421455144882</v>
+        <v>5941.465822935104</v>
       </c>
       <c r="D6" t="n">
-        <v>9.760000228881836</v>
+        <v>5.5</v>
       </c>
       <c r="E6" t="n">
-        <v>2.783389270305633</v>
+        <v>2.713243058387269</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9101040363311768</v>
+        <v>0.9151785969734192</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9357638955116272</v>
+        <v>0.9268077611923218</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9347921013832092</v>
+        <v>0.9276896119117736</v>
       </c>
       <c r="I6" t="n">
-        <v>0.929801344871521</v>
+        <v>0.9300265908241272</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4633772373199463</v>
+        <v>0.5323563814163208</v>
       </c>
       <c r="K6" t="n">
-        <v>237.7907571792603</v>
+        <v>93.12863183021544</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2092164462467409</v>
+        <v>0.1774338416333468</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4522299586601977</v>
+        <v>0.3536465932738106</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3871189918158189</v>
+        <v>0.3348114715432221</v>
       </c>
       <c r="O6" t="n">
-        <v>11.08847165107727</v>
+        <v>9.403993606567385</v>
       </c>
       <c r="P6" t="n">
-        <v>23.96818780899048</v>
+        <v>18.74326944351196</v>
       </c>
       <c r="Q6" t="n">
-        <v>20.5173065662384</v>
+        <v>17.74500799179077</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250630-112532</t>
+          <t>20250728-180542</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -5780,22 +5780,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -5993,56 +5993,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C2" t="n">
-        <v>2489.299755334854</v>
+        <v>5269.247237443924</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5</v>
+        <v>7.960000038146973</v>
       </c>
       <c r="E2" t="n">
-        <v>2.868917557928297</v>
+        <v>2.797472953796387</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8834080696105957</v>
+        <v>0.9241982698440552</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9209261536598206</v>
+        <v>0.9514647722244264</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9198237657546996</v>
+        <v>0.9488412737846376</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8878302574157715</v>
+        <v>0.936487078666687</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4911258518695831</v>
+        <v>0.4599054157733917</v>
       </c>
       <c r="K2" t="n">
-        <v>93.73305559158324</v>
+        <v>380.3847172260285</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1813471587199085</v>
+        <v>0.1746297107552582</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3745147192253257</v>
+        <v>0.4349905859749272</v>
       </c>
       <c r="N2" t="n">
-        <v>0.349353515876914</v>
+        <v>0.5797317522876667</v>
       </c>
       <c r="O2" t="n">
-        <v>9.611399412155151</v>
+        <v>9.255374670028688</v>
       </c>
       <c r="P2" t="n">
-        <v>19.84928011894226</v>
+        <v>23.05450105667114</v>
       </c>
       <c r="Q2" t="n">
-        <v>18.51573634147644</v>
+        <v>30.72578287124633</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250630-211456</t>
+          <t>20250729-154516</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -6052,7 +6052,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -6067,22 +6067,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -6114,56 +6114,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="C3" t="n">
-        <v>2319.881287813186</v>
+        <v>5489.370683670044</v>
       </c>
       <c r="D3" t="n">
-        <v>3.359999895095825</v>
+        <v>8.100000381469727</v>
       </c>
       <c r="E3" t="n">
-        <v>2.806609686683206</v>
+        <v>2.78267616885049</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8807822465896606</v>
+        <v>0.9229651093482972</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9083594083786012</v>
+        <v>0.9449225664138794</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9089293479919434</v>
+        <v>0.9446367025375366</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9011086225509644</v>
+        <v>0.9390997290611268</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6658132076263428</v>
+        <v>0.4665795862674713</v>
       </c>
       <c r="K3" t="n">
-        <v>93.04939317703248</v>
+        <v>153.0331523418427</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2236717826915237</v>
+        <v>0.1812651562240888</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3740244136666352</v>
+        <v>0.3712336882105413</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3365122912065038</v>
+        <v>0.3816079823475963</v>
       </c>
       <c r="O3" t="n">
-        <v>11.85460448265076</v>
+        <v>9.607053279876707</v>
       </c>
       <c r="P3" t="n">
-        <v>19.82329392433167</v>
+        <v>19.67538547515869</v>
       </c>
       <c r="Q3" t="n">
-        <v>17.8351514339447</v>
+        <v>20.22522306442261</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250630-215925</t>
+          <t>20250729-172122</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -6188,22 +6188,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -6235,56 +6235,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="C4" t="n">
-        <v>2255.941898345948</v>
+        <v>6058.982568979263</v>
       </c>
       <c r="D4" t="n">
-        <v>3.220000028610229</v>
+        <v>8.710000038146973</v>
       </c>
       <c r="E4" t="n">
-        <v>2.738303619272568</v>
+        <v>2.758430379502317</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8761484622955322</v>
+        <v>0.9232439994812012</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9075704216957092</v>
+        <v>0.9525880813598632</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9056939482688904</v>
+        <v>0.9510917067527772</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9055755138397216</v>
+        <v>0.9458987712860109</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6540232300758362</v>
+        <v>0.4577480554580688</v>
       </c>
       <c r="K4" t="n">
-        <v>92.61390781402588</v>
+        <v>161.5108454227448</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2183145487083579</v>
+        <v>0.1732607427633033</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3401970188572721</v>
+        <v>0.363453023838547</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3415415961787386</v>
+        <v>0.3703275536591152</v>
       </c>
       <c r="O4" t="n">
-        <v>11.57067108154297</v>
+        <v>9.182819366455078</v>
       </c>
       <c r="P4" t="n">
-        <v>18.03044199943542</v>
+        <v>19.263010263443</v>
       </c>
       <c r="Q4" t="n">
-        <v>18.10170459747314</v>
+        <v>19.62736034393311</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250630-224121</t>
+          <t>20250729-185705</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -6309,22 +6309,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -6356,56 +6356,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="C5" t="n">
-        <v>2367.214252471924</v>
+        <v>5786.023115873337</v>
       </c>
       <c r="D5" t="n">
-        <v>3.319999933242798</v>
+        <v>8.140000343322754</v>
       </c>
       <c r="E5" t="n">
-        <v>2.714908189243741</v>
+        <v>2.747350226508246</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8868913650512695</v>
+        <v>0.9273660778999328</v>
       </c>
       <c r="G5" t="n">
-        <v>0.920691192150116</v>
+        <v>0.9510186314582824</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9228723645210266</v>
+        <v>0.95039165019989</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9106345176696776</v>
+        <v>0.945026159286499</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5375298261642456</v>
+        <v>0.4675171375274658</v>
       </c>
       <c r="K5" t="n">
-        <v>92.30909132957458</v>
+        <v>155.6258144378662</v>
       </c>
       <c r="L5" t="n">
-        <v>0.185865600154085</v>
+        <v>0.1817101172681124</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3614584544919572</v>
+        <v>0.3712570982159309</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3470903117701692</v>
+        <v>0.3554677468425822</v>
       </c>
       <c r="O5" t="n">
-        <v>9.850876808166504</v>
+        <v>9.630636215209959</v>
       </c>
       <c r="P5" t="n">
-        <v>19.15729808807373</v>
+        <v>19.67662620544434</v>
       </c>
       <c r="Q5" t="n">
-        <v>18.39578652381897</v>
+        <v>18.83979058265686</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250630-232211</t>
+          <t>20250729-204219</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -6430,22 +6430,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -6477,56 +6477,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C6" t="n">
-        <v>2116.042106866837</v>
+        <v>3785.693192243576</v>
       </c>
       <c r="D6" t="n">
-        <v>3.410000085830688</v>
+        <v>8.119999885559082</v>
       </c>
       <c r="E6" t="n">
-        <v>2.722084239125252</v>
+        <v>2.750902488313872</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8781038522720337</v>
+        <v>0.915582001209259</v>
       </c>
       <c r="G6" t="n">
-        <v>0.916999578475952</v>
+        <v>0.943711519241333</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9195710420608521</v>
+        <v>0.9414355158805848</v>
       </c>
       <c r="I6" t="n">
-        <v>0.910284459590912</v>
+        <v>0.9355400800704956</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6602791547775269</v>
+        <v>0.4598429203033447</v>
       </c>
       <c r="K6" t="n">
-        <v>100.2173683643341</v>
+        <v>152.3776657581329</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2082032707502257</v>
+        <v>0.1731607374155296</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3753677674059598</v>
+        <v>0.3817240742017638</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3312347879949606</v>
+        <v>0.3732160847142057</v>
       </c>
       <c r="O6" t="n">
-        <v>11.03477334976196</v>
+        <v>9.177519083023071</v>
       </c>
       <c r="P6" t="n">
-        <v>19.89449167251587</v>
+        <v>20.23137593269348</v>
       </c>
       <c r="Q6" t="n">
-        <v>17.55544376373291</v>
+        <v>19.78045248985291</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-000435</t>
+          <t>20250729-222305</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -6551,22 +6551,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -6764,56 +6764,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20</v>
+        <v>83</v>
       </c>
       <c r="C2" t="n">
-        <v>2626.311824321747</v>
+        <v>2668.701236009598</v>
       </c>
       <c r="D2" t="n">
-        <v>7.849999904632568</v>
+        <v>10.60999965667725</v>
       </c>
       <c r="E2" t="n">
-        <v>2.710729193687439</v>
+        <v>1.341375277703067</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9139314293861388</v>
+        <v>0.8196969628334045</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9416846632957458</v>
+        <v>0.8711385726928711</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9425981640815736</v>
+        <v>0.8660994172096252</v>
       </c>
       <c r="I2" t="n">
-        <v>0.937198042869568</v>
+        <v>0.864164412021637</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5018670558929443</v>
+        <v>0.3487617671489715</v>
       </c>
       <c r="K2" t="n">
-        <v>167.69322681427</v>
+        <v>58.11624002456665</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1959977374886566</v>
+        <v>0.1190329632669125</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3898388709662095</v>
+        <v>0.3267967880896802</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3799602310612516</v>
+        <v>0.3086352078419811</v>
       </c>
       <c r="O2" t="n">
-        <v>10.3878800868988</v>
+        <v>6.308747053146362</v>
       </c>
       <c r="P2" t="n">
-        <v>20.6614601612091</v>
+        <v>17.32022976875305</v>
       </c>
       <c r="Q2" t="n">
-        <v>20.13789224624633</v>
+        <v>16.357666015625</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-103708</t>
+          <t>20250730-134317</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -6823,7 +6823,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -6838,22 +6838,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -6885,56 +6885,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17</v>
+        <v>74</v>
       </c>
       <c r="C3" t="n">
-        <v>2333.70684337616</v>
+        <v>2307.560757875443</v>
       </c>
       <c r="D3" t="n">
-        <v>6.849999904632568</v>
+        <v>10.63000011444092</v>
       </c>
       <c r="E3" t="n">
-        <v>2.81048864476821</v>
+        <v>1.294306621358201</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9102373719215392</v>
+        <v>0.795487642288208</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9367640614509584</v>
+        <v>0.8445748090744019</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9363001585006714</v>
+        <v>0.8434897065162659</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9269812703132628</v>
+        <v>0.8471001982688904</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5318329930305481</v>
+        <v>0.314994752407074</v>
       </c>
       <c r="K3" t="n">
-        <v>156.0113439559937</v>
+        <v>58.33678412437439</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2008039366524174</v>
+        <v>0.117289219262465</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3923259996018319</v>
+        <v>0.310893621084825</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3710939029477677</v>
+        <v>0.2990662196897111</v>
       </c>
       <c r="O3" t="n">
-        <v>10.64260864257812</v>
+        <v>6.216328620910645</v>
       </c>
       <c r="P3" t="n">
-        <v>20.79327797889709</v>
+        <v>16.47736191749573</v>
       </c>
       <c r="Q3" t="n">
-        <v>19.66797685623169</v>
+        <v>15.85050964355469</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-112519</t>
+          <t>20250730-142951</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -6959,22 +6959,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -7006,56 +7006,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>98</v>
       </c>
       <c r="C4" t="n">
-        <v>2716.914121866226</v>
+        <v>3084.45719742775</v>
       </c>
       <c r="D4" t="n">
-        <v>7.630000114440918</v>
+        <v>10.6899995803833</v>
       </c>
       <c r="E4" t="n">
-        <v>2.814272594451904</v>
+        <v>1.315792846436403</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9039589166641236</v>
+        <v>0.8152050971984863</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9410211443901062</v>
+        <v>0.8638373017311096</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9400880932807922</v>
+        <v>0.8642193675041199</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9394073486328124</v>
+        <v>0.8656455278396606</v>
       </c>
       <c r="J4" t="n">
-        <v>0.65604567527771</v>
+        <v>0.3047914803028106</v>
       </c>
       <c r="K4" t="n">
-        <v>154.1732475757599</v>
+        <v>65.18516373634338</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2301827286774257</v>
+        <v>0.1127616099591525</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4057054654607233</v>
+        <v>0.3097823925738064</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3638221857682714</v>
+        <v>0.2958108299183395</v>
       </c>
       <c r="O4" t="n">
-        <v>12.19968461990356</v>
+        <v>5.976365327835083</v>
       </c>
       <c r="P4" t="n">
-        <v>21.50238966941833</v>
+        <v>16.41846680641174</v>
       </c>
       <c r="Q4" t="n">
-        <v>19.28257584571838</v>
+        <v>15.677973985672</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-120828</t>
+          <t>20250730-151039</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -7080,22 +7080,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -7127,56 +7127,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="C5" t="n">
-        <v>2717.347125768661</v>
+        <v>1781.695658683777</v>
       </c>
       <c r="D5" t="n">
-        <v>6.900000095367432</v>
+        <v>10.64000034332275</v>
       </c>
       <c r="E5" t="n">
-        <v>2.806224858760834</v>
+        <v>1.307494891541345</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9205419421195984</v>
+        <v>0.7966039180755615</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9413823485374452</v>
+        <v>0.837837815284729</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9413823485374452</v>
+        <v>0.8392156958580017</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9414355158805848</v>
+        <v>0.8400349617004395</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5170595645904541</v>
+        <v>0.300374299287796</v>
       </c>
       <c r="K5" t="n">
-        <v>161.5577793121338</v>
+        <v>64.66937518119812</v>
       </c>
       <c r="L5" t="n">
-        <v>0.203315406475427</v>
+        <v>0.1188478199940807</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3960806873609435</v>
+        <v>0.3267043176686989</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3794450984810883</v>
+        <v>0.3065480106281784</v>
       </c>
       <c r="O5" t="n">
-        <v>10.77571654319763</v>
+        <v>6.298934459686279</v>
       </c>
       <c r="P5" t="n">
-        <v>20.99227643013</v>
+        <v>17.31532883644104</v>
       </c>
       <c r="Q5" t="n">
-        <v>20.11059021949768</v>
+        <v>16.24704456329346</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-125809</t>
+          <t>20250730-160424</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -7201,22 +7201,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -7248,56 +7248,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>98</v>
       </c>
       <c r="C6" t="n">
-        <v>2179.526694297791</v>
+        <v>3043.011875152588</v>
       </c>
       <c r="D6" t="n">
-        <v>7.159999847412109</v>
+        <v>10.77999973297119</v>
       </c>
       <c r="E6" t="n">
-        <v>2.777593120932579</v>
+        <v>1.291676428853249</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9149709343910216</v>
+        <v>0.818816602230072</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9429323673248292</v>
+        <v>0.8650726079940796</v>
       </c>
       <c r="H6" t="n">
-        <v>0.942105233669281</v>
+        <v>0.8617957830429077</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9380530714988708</v>
+        <v>0.8632966876029968</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6427344679832458</v>
+        <v>0.3493632972240448</v>
       </c>
       <c r="K6" t="n">
-        <v>156.1998476982117</v>
+        <v>58.71957802772522</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2153910960791246</v>
+        <v>0.1184770026296939</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3772290202806581</v>
+        <v>0.3310341295206321</v>
       </c>
       <c r="N6" t="n">
-        <v>0.366157387787441</v>
+        <v>0.3095921210522921</v>
       </c>
       <c r="O6" t="n">
-        <v>11.4157280921936</v>
+        <v>6.279281139373779</v>
       </c>
       <c r="P6" t="n">
-        <v>19.99313807487488</v>
+        <v>17.54480886459351</v>
       </c>
       <c r="Q6" t="n">
-        <v>19.40634155273437</v>
+        <v>16.40838241577148</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-134746</t>
+          <t>20250730-163628</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -7322,22 +7322,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -7535,56 +7535,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="C2" t="n">
-        <v>1621.086301803589</v>
+        <v>883.5669202804565</v>
       </c>
       <c r="D2" t="n">
-        <v>2.240000009536743</v>
+        <v>14</v>
       </c>
       <c r="E2" t="n">
-        <v>1.012963052896353</v>
+        <v>0.7770239561796188</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8782707452774048</v>
+        <v>0.9179023504257202</v>
       </c>
       <c r="G2" t="n">
-        <v>0.926151156425476</v>
+        <v>0.9402079582214355</v>
       </c>
       <c r="H2" t="n">
-        <v>0.926151156425476</v>
+        <v>0.941074550151825</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9286971688270568</v>
+        <v>0.9191526174545288</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3888917565345764</v>
+        <v>0.2196117937564849</v>
       </c>
       <c r="K2" t="n">
-        <v>50.17802834510803</v>
+        <v>137.655834197998</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1521381252216843</v>
+        <v>0.1075816739280268</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4047925967090535</v>
+        <v>0.3620184592480929</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3410672736617754</v>
+        <v>0.3444619763572261</v>
       </c>
       <c r="O2" t="n">
-        <v>8.063320636749268</v>
+        <v>5.701828718185425</v>
       </c>
       <c r="P2" t="n">
-        <v>21.45400762557984</v>
+        <v>19.18697834014893</v>
       </c>
       <c r="Q2" t="n">
-        <v>18.0765655040741</v>
+        <v>18.25648474693298</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-214805</t>
+          <t>20250731-052933</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -7609,22 +7609,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -7656,56 +7656,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>107</v>
+        <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>2588.516779184341</v>
+        <v>1008.547520637512</v>
       </c>
       <c r="D3" t="n">
-        <v>2.640000104904175</v>
+        <v>13.65999984741211</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9860311211826646</v>
+        <v>0.7824210870265961</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8865593671798706</v>
+        <v>0.9382986426353456</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9368653297424316</v>
+        <v>0.9537648558616638</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9369210600852966</v>
+        <v>0.9524229168891908</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9362637400627136</v>
+        <v>0.9460289478302002</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4074293673038482</v>
+        <v>0.2132528126239776</v>
       </c>
       <c r="K3" t="n">
-        <v>47.11515879631042</v>
+        <v>102.6456184387207</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1442316118276344</v>
+        <v>0.1119669428411519</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3685655368948882</v>
+        <v>0.3473830313052771</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3230140838982924</v>
+        <v>0.3477679558520047</v>
       </c>
       <c r="O3" t="n">
-        <v>7.644275426864624</v>
+        <v>5.934247970581055</v>
       </c>
       <c r="P3" t="n">
-        <v>19.53397345542908</v>
+        <v>18.41130065917969</v>
       </c>
       <c r="Q3" t="n">
-        <v>17.1197464466095</v>
+        <v>18.43170166015625</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-221718</t>
+          <t>20250731-054803</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -7715,7 +7715,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -7730,22 +7730,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -7777,56 +7777,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C4" t="n">
-        <v>2015.971925735474</v>
+        <v>1258.567029237747</v>
       </c>
       <c r="D4" t="n">
-        <v>2.309999942779541</v>
+        <v>13.97999954223633</v>
       </c>
       <c r="E4" t="n">
-        <v>1.030864205956459</v>
+        <v>0.7451312000934894</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8774341344833374</v>
+        <v>0.9431072473526</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9307624697685242</v>
+        <v>0.9534984827041626</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9290717840194702</v>
+        <v>0.9517601132392884</v>
       </c>
       <c r="I4" t="n">
-        <v>0.931518852710724</v>
+        <v>0.9423580765724182</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3881617188453674</v>
+        <v>0.2802190482616424</v>
       </c>
       <c r="K4" t="n">
-        <v>41.77544522285461</v>
+        <v>117.4765841960907</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1408783804695561</v>
+        <v>0.1136572540930982</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3243442841295926</v>
+        <v>0.3594768092317401</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3191123953405416</v>
+        <v>0.3686044486063831</v>
       </c>
       <c r="O4" t="n">
-        <v>7.466554164886475</v>
+        <v>6.023834466934204</v>
       </c>
       <c r="P4" t="n">
-        <v>17.19024705886841</v>
+        <v>19.05227088928223</v>
       </c>
       <c r="Q4" t="n">
-        <v>16.91295695304871</v>
+        <v>19.53603577613831</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-230237</t>
+          <t>20250731-060809</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -7851,22 +7851,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -7898,56 +7898,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>92</v>
+        <v>41</v>
       </c>
       <c r="C5" t="n">
-        <v>2197.988644361496</v>
+        <v>826.3118932247162</v>
       </c>
       <c r="D5" t="n">
-        <v>2.619999885559082</v>
+        <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9736849121425464</v>
+        <v>0.7798704461353582</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8814066648483276</v>
+        <v>0.9373855590820312</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9333917498588562</v>
+        <v>0.9439088702201844</v>
       </c>
       <c r="H5" t="n">
-        <v>0.933920681476593</v>
+        <v>0.9447852969169616</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9346866607666016</v>
+        <v>0.9424083828926086</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3917684257030487</v>
+        <v>0.2066398411989212</v>
       </c>
       <c r="K5" t="n">
-        <v>40.81873154640198</v>
+        <v>125.2589178085327</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1438748566609508</v>
+        <v>0.1054598295463705</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3617163514191249</v>
+        <v>0.3633521053026307</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3169751887051564</v>
+        <v>0.3399848128264805</v>
       </c>
       <c r="O5" t="n">
-        <v>7.625367403030396</v>
+        <v>5.589370965957642</v>
       </c>
       <c r="P5" t="n">
-        <v>19.17096662521362</v>
+        <v>19.25766158103943</v>
       </c>
       <c r="Q5" t="n">
-        <v>16.79968500137329</v>
+        <v>18.01919507980347</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-233821</t>
+          <t>20250731-063225</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -7972,22 +7972,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -8019,56 +8019,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="C6" t="n">
-        <v>1299.961209774017</v>
+        <v>1293.56325507164</v>
       </c>
       <c r="D6" t="n">
-        <v>2.200000047683716</v>
+        <v>14.22000026702881</v>
       </c>
       <c r="E6" t="n">
-        <v>1.054464538097382</v>
+        <v>0.7715477723341722</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8780303001403809</v>
+        <v>0.9438849091529846</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9332153797149658</v>
+        <v>0.9555749297142028</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9328621625900269</v>
+        <v>0.957317054271698</v>
       </c>
       <c r="I6" t="n">
-        <v>0.932683765888214</v>
+        <v>0.9548611044883728</v>
       </c>
       <c r="J6" t="n">
-        <v>0.285345196723938</v>
+        <v>0.2428148090839386</v>
       </c>
       <c r="K6" t="n">
-        <v>45.85628986358643</v>
+        <v>97.38323354721069</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1271274359721058</v>
+        <v>0.1089483881896396</v>
       </c>
       <c r="M6" t="n">
-        <v>0.35711333436786</v>
+        <v>0.3598885221301384</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3126104417836891</v>
+        <v>0.3542447854887764</v>
       </c>
       <c r="O6" t="n">
-        <v>6.737754106521606</v>
+        <v>5.774264574050903</v>
       </c>
       <c r="P6" t="n">
-        <v>18.92700672149659</v>
+        <v>19.07409167289734</v>
       </c>
       <c r="Q6" t="n">
-        <v>16.56835341453552</v>
+        <v>18.77497363090515</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250702-001708</t>
+          <t>20250731-064935</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -8093,22 +8093,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -8306,56 +8306,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>116</v>
+        <v>38</v>
       </c>
       <c r="C2" t="n">
-        <v>3650.076964139937</v>
+        <v>492.7823739051819</v>
       </c>
       <c r="D2" t="n">
-        <v>5.579999923706055</v>
+        <v>6.849999904632568</v>
       </c>
       <c r="E2" t="n">
-        <v>1.315986197570275</v>
+        <v>0.4864118710944527</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8203592896461487</v>
+        <v>0.8366873264312744</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8748921751976013</v>
+        <v>0.905825674533844</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8721340298652649</v>
+        <v>0.905825674533844</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8735125660896301</v>
+        <v>0.9070568084716796</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3214545845985412</v>
+        <v>0.3278024196624756</v>
       </c>
       <c r="K2" t="n">
-        <v>59.00357437133789</v>
+        <v>73.01832604408264</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1179523737925403</v>
+        <v>0.1133985159532079</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3050718307495117</v>
+        <v>0.3368128920501133</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2925819091077121</v>
+        <v>0.3145395674795475</v>
       </c>
       <c r="O2" t="n">
-        <v>6.251475811004639</v>
+        <v>6.01012134552002</v>
       </c>
       <c r="P2" t="n">
-        <v>16.16880702972412</v>
+        <v>17.85108327865601</v>
       </c>
       <c r="Q2" t="n">
-        <v>15.50684118270874</v>
+        <v>16.67059707641602</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250702-125220</t>
+          <t>20250627-180617</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -8427,56 +8427,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>98</v>
+        <v>29</v>
       </c>
       <c r="C3" t="n">
-        <v>3137.838816404343</v>
+        <v>365.562046289444</v>
       </c>
       <c r="D3" t="n">
-        <v>5.590000152587891</v>
+        <v>6.690000057220459</v>
       </c>
       <c r="E3" t="n">
-        <v>1.334623269888819</v>
+        <v>0.4638315480330894</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8293224573135376</v>
+        <v>0.8332052230834961</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8607484698295593</v>
+        <v>0.9031111001968384</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8517520427703857</v>
+        <v>0.903598427772522</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8557435274124146</v>
+        <v>0.9037693738937378</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3163049519062042</v>
+        <v>0.2948665022850036</v>
       </c>
       <c r="K3" t="n">
-        <v>60.02398252487183</v>
+        <v>72.97705483436584</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1158834448400533</v>
+        <v>0.1094226342327189</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3160213569425187</v>
+        <v>0.3289148987464185</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3034860278075596</v>
+        <v>0.3193834187849512</v>
       </c>
       <c r="O3" t="n">
-        <v>6.141822576522827</v>
+        <v>5.799399614334106</v>
       </c>
       <c r="P3" t="n">
-        <v>16.74913191795349</v>
+        <v>17.43248963356018</v>
       </c>
       <c r="Q3" t="n">
-        <v>16.08475947380066</v>
+        <v>16.92732119560242</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250702-135530</t>
+          <t>20250627-181706</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -8548,56 +8548,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>98</v>
+        <v>32</v>
       </c>
       <c r="C4" t="n">
-        <v>3016.639753341675</v>
+        <v>418.8017570972443</v>
       </c>
       <c r="D4" t="n">
-        <v>5.710000038146973</v>
+        <v>7.210000038146973</v>
       </c>
       <c r="E4" t="n">
-        <v>1.284500833676786</v>
+        <v>0.4873544313013553</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8225686550140381</v>
+        <v>0.8269375562667847</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8808063268661499</v>
+        <v>0.8818897604942322</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8757238388061523</v>
+        <v>0.8824814558029175</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8756086826324463</v>
+        <v>0.882867157459259</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3166313469409942</v>
+        <v>0.326488196849823</v>
       </c>
       <c r="K4" t="n">
-        <v>57.5421130657196</v>
+        <v>71.84800410270691</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1178937048282263</v>
+        <v>0.1128520605699071</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2990082254949606</v>
+        <v>0.3298849789601452</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2941042972060869</v>
+        <v>0.3210471126268495</v>
       </c>
       <c r="O4" t="n">
-        <v>6.248366355895996</v>
+        <v>5.981159210205078</v>
       </c>
       <c r="P4" t="n">
-        <v>15.84743595123291</v>
+        <v>17.4839038848877</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.58752775192261</v>
+        <v>17.01549696922302</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250702-144954</t>
+          <t>20250627-182547</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -8607,7 +8607,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -8669,56 +8669,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="C5" t="n">
-        <v>3618.868261575699</v>
+        <v>570.5052013397217</v>
       </c>
       <c r="D5" t="n">
-        <v>5.78000020980835</v>
+        <v>6.860000133514404</v>
       </c>
       <c r="E5" t="n">
-        <v>1.303238579939152</v>
+        <v>0.4828944477167996</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8315358757972717</v>
+        <v>0.8375339508056641</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8788142800331116</v>
+        <v>0.908450722694397</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8753880262374878</v>
+        <v>0.9066901206970216</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8755516409873962</v>
+        <v>0.9050132036209106</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3339658379554748</v>
+        <v>0.3125357627868652</v>
       </c>
       <c r="K5" t="n">
-        <v>59.21383261680603</v>
+        <v>77.45805501937866</v>
       </c>
       <c r="L5" t="n">
-        <v>0.117859404042082</v>
+        <v>0.1095531976447915</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3073550305276546</v>
+        <v>0.3311687145593031</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2946352373878911</v>
+        <v>0.3275613829774677</v>
       </c>
       <c r="O5" t="n">
-        <v>6.246548414230347</v>
+        <v>5.80631947517395</v>
       </c>
       <c r="P5" t="n">
-        <v>16.2898166179657</v>
+        <v>17.55194187164307</v>
       </c>
       <c r="Q5" t="n">
-        <v>15.61566758155823</v>
+        <v>17.36075329780579</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250702-154230</t>
+          <t>20250627-183521</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -8790,56 +8790,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>131</v>
+        <v>29</v>
       </c>
       <c r="C6" t="n">
-        <v>4101.407125473023</v>
+        <v>391.9583246707916</v>
       </c>
       <c r="D6" t="n">
-        <v>5.760000228881836</v>
+        <v>6.860000133514404</v>
       </c>
       <c r="E6" t="n">
-        <v>1.309732409833952</v>
+        <v>0.5020293891429901</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8526551723480225</v>
+        <v>0.8460966348648071</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8901581764221191</v>
+        <v>0.9007833003997804</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8926204442977905</v>
+        <v>0.9003914594650269</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8980132341384888</v>
+        <v>0.8975609540939331</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2988329231739044</v>
+        <v>0.2807487845420837</v>
       </c>
       <c r="K6" t="n">
-        <v>59.73193764686584</v>
+        <v>73.52596306800842</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1144514173831579</v>
+        <v>0.1119329614459343</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3169315221174708</v>
+        <v>0.3340092020214729</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3061027706794019</v>
+        <v>0.3209806658187003</v>
       </c>
       <c r="O6" t="n">
-        <v>6.065925121307373</v>
+        <v>5.932446956634521</v>
       </c>
       <c r="P6" t="n">
-        <v>16.79737067222595</v>
+        <v>17.70248770713806</v>
       </c>
       <c r="Q6" t="n">
-        <v>16.2234468460083</v>
+        <v>17.01197528839111</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250702-164509</t>
+          <t>20250627-184722</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -9077,56 +9077,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C2" t="n">
-        <v>1230.48997926712</v>
+        <v>1621.086301803589</v>
       </c>
       <c r="D2" t="n">
-        <v>8.649999618530273</v>
+        <v>2.240000009536743</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7664731221814309</v>
+        <v>1.012963052896353</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9217018485069276</v>
+        <v>0.8782707452774048</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9312910437583924</v>
+        <v>0.926151156425476</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9331001043319702</v>
+        <v>0.926151156425476</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8908406496047974</v>
+        <v>0.9286971688270568</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2522724568843841</v>
+        <v>0.3888917565345764</v>
       </c>
       <c r="K2" t="n">
-        <v>123.2327589988708</v>
+        <v>50.17802834510803</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1356653177513266</v>
+        <v>0.1521381252216843</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3561544733227424</v>
+        <v>0.4047925967090535</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3522831358999576</v>
+        <v>0.3410672736617754</v>
       </c>
       <c r="O2" t="n">
-        <v>7.190261840820312</v>
+        <v>8.063320636749268</v>
       </c>
       <c r="P2" t="n">
-        <v>18.87618708610535</v>
+        <v>21.45400762557984</v>
       </c>
       <c r="Q2" t="n">
-        <v>18.67100620269776</v>
+        <v>18.0765655040741</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250703-135522</t>
+          <t>20250701-214805</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -9198,56 +9198,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>50</v>
+        <v>107</v>
       </c>
       <c r="C3" t="n">
-        <v>990.8793737888336</v>
+        <v>2588.516779184341</v>
       </c>
       <c r="D3" t="n">
-        <v>8.340000152587891</v>
+        <v>2.640000104904175</v>
       </c>
       <c r="E3" t="n">
-        <v>0.757763524055481</v>
+        <v>0.9860311211826646</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9368382692337036</v>
+        <v>0.8865593671798706</v>
       </c>
       <c r="G3" t="n">
-        <v>0.946076273918152</v>
+        <v>0.9368653297424316</v>
       </c>
       <c r="H3" t="n">
-        <v>0.946906566619873</v>
+        <v>0.9369210600852966</v>
       </c>
       <c r="I3" t="n">
-        <v>0.940397322177887</v>
+        <v>0.9362637400627136</v>
       </c>
       <c r="J3" t="n">
-        <v>0.395474374294281</v>
+        <v>0.4074293673038482</v>
       </c>
       <c r="K3" t="n">
-        <v>109.7282929420471</v>
+        <v>47.11515879631042</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1546133329283516</v>
+        <v>0.1442316118276344</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3628341027025906</v>
+        <v>0.3685655368948882</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3532669949081709</v>
+        <v>0.3230140838982924</v>
       </c>
       <c r="O3" t="n">
-        <v>8.194506645202637</v>
+        <v>7.644275426864624</v>
       </c>
       <c r="P3" t="n">
-        <v>19.2302074432373</v>
+        <v>19.53397345542908</v>
       </c>
       <c r="Q3" t="n">
-        <v>18.72315073013306</v>
+        <v>17.1197464466095</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250703-141918</t>
+          <t>20250701-221718</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -9319,56 +9319,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="C4" t="n">
-        <v>885.8357172012329</v>
+        <v>2015.971925735474</v>
       </c>
       <c r="D4" t="n">
-        <v>8.529999732971191</v>
+        <v>2.309999942779541</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7742426666346464</v>
+        <v>1.030864205956459</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9363995790481568</v>
+        <v>0.8774341344833374</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9480175971984864</v>
+        <v>0.9307624697685242</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9493168592453004</v>
+        <v>0.9290717840194702</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9483362436294556</v>
+        <v>0.931518852710724</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4207412302494049</v>
+        <v>0.3881617188453674</v>
       </c>
       <c r="K4" t="n">
-        <v>115.1350932121277</v>
+        <v>41.77544522285461</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1581602006588342</v>
+        <v>0.1408783804695561</v>
       </c>
       <c r="M4" t="n">
-        <v>0.355458250585592</v>
+        <v>0.3243442841295926</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3680162969625221</v>
+        <v>0.3191123953405416</v>
       </c>
       <c r="O4" t="n">
-        <v>8.382490634918213</v>
+        <v>7.466554164886475</v>
       </c>
       <c r="P4" t="n">
-        <v>18.83928728103638</v>
+        <v>17.19024705886841</v>
       </c>
       <c r="Q4" t="n">
-        <v>19.50486373901367</v>
+        <v>16.91295695304871</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250703-143912</t>
+          <t>20250701-230237</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -9440,56 +9440,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="C5" t="n">
-        <v>828.2476706504822</v>
+        <v>2197.988644361496</v>
       </c>
       <c r="D5" t="n">
-        <v>8.170000076293945</v>
+        <v>2.619999885559082</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7785944880508795</v>
+        <v>0.9736849121425464</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9286764860153198</v>
+        <v>0.8814066648483276</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9475982785224916</v>
+        <v>0.9333917498588562</v>
       </c>
       <c r="H5" t="n">
-        <v>0.947138488292694</v>
+        <v>0.933920681476593</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9449300765991212</v>
+        <v>0.9346866607666016</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4105097353458404</v>
+        <v>0.3917684257030487</v>
       </c>
       <c r="K5" t="n">
-        <v>99.07067036628725</v>
+        <v>40.81873154640198</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1548971275113663</v>
+        <v>0.1438748566609508</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3619616706416292</v>
+        <v>0.3617163514191249</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3615950458454636</v>
+        <v>0.3169751887051564</v>
       </c>
       <c r="O5" t="n">
-        <v>8.209547758102417</v>
+        <v>7.625367403030396</v>
       </c>
       <c r="P5" t="n">
-        <v>19.18396854400635</v>
+        <v>19.17096662521362</v>
       </c>
       <c r="Q5" t="n">
-        <v>19.16453742980957</v>
+        <v>16.79968500137329</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250703-145727</t>
+          <t>20250701-233821</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -9499,7 +9499,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -9561,56 +9561,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="C6" t="n">
-        <v>1166.700079917907</v>
+        <v>1299.961209774017</v>
       </c>
       <c r="D6" t="n">
-        <v>8.090000152587891</v>
+        <v>2.200000047683716</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7677391009815668</v>
+        <v>1.054464538097382</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9403148889541626</v>
+        <v>0.8780303001403809</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9527524709701538</v>
+        <v>0.9332153797149658</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9537925124168396</v>
+        <v>0.9328621625900269</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9529616832733154</v>
+        <v>0.932683765888214</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4135887622833252</v>
+        <v>0.285345196723938</v>
       </c>
       <c r="K6" t="n">
-        <v>114.4814584255218</v>
+        <v>45.85628986358643</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1576135743339106</v>
+        <v>0.1271274359721058</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3588852927369891</v>
+        <v>0.35711333436786</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3475386916466479</v>
+        <v>0.3126104417836891</v>
       </c>
       <c r="O6" t="n">
-        <v>8.353519439697266</v>
+        <v>6.737754106521606</v>
       </c>
       <c r="P6" t="n">
-        <v>19.02092051506042</v>
+        <v>18.92700672149659</v>
       </c>
       <c r="Q6" t="n">
-        <v>18.41955065727234</v>
+        <v>16.56835341453552</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250703-151429</t>
+          <t>20250702-001708</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -9620,7 +9620,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
